--- a/Experiments/outputs/scenario_4.xlsx
+++ b/Experiments/outputs/scenario_4.xlsx
@@ -530,55 +530,55 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2560.098892073896</v>
+        <v>2597.153525734425</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8418838977813721</v>
+        <v>1.195918798446655</v>
       </c>
       <c r="E2" t="n">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="F2" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G2" t="n">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="H2" t="n">
-        <v>2850.20359133025</v>
+        <v>2808.720105122139</v>
       </c>
       <c r="I2" t="n">
-        <v>2.108611822128296</v>
+        <v>12.42775392532349</v>
       </c>
       <c r="J2" t="n">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="K2" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="L2" t="n">
-        <v>516</v>
+        <v>614</v>
       </c>
       <c r="M2" t="n">
-        <v>5357.223825311906</v>
+        <v>5213.883030873595</v>
       </c>
       <c r="N2" t="n">
-        <v>8.554233074188232</v>
+        <v>5.489766836166382</v>
       </c>
       <c r="O2" t="n">
-        <v>1652</v>
+        <v>1882</v>
       </c>
       <c r="P2" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="Q2" t="n">
-        <v>5071</v>
+        <v>5821</v>
       </c>
       <c r="R2" t="n">
-        <v>0.5221220961540013</v>
+        <v>0.5018772936877205</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4679700374168506</v>
+        <v>0.4612997475220435</v>
       </c>
     </row>
     <row r="3">
@@ -591,55 +591,55 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2588.373556953156</v>
+        <v>2602.490091365411</v>
       </c>
       <c r="D3" t="n">
-        <v>1.21083927154541</v>
+        <v>0.9860990047454834</v>
       </c>
       <c r="E3" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F3" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G3" t="n">
         <v>109</v>
       </c>
       <c r="H3" t="n">
-        <v>2819.316008199801</v>
+        <v>2830.931283426666</v>
       </c>
       <c r="I3" t="n">
-        <v>3.392852067947388</v>
+        <v>12.7275869846344</v>
       </c>
       <c r="J3" t="n">
-        <v>467</v>
+        <v>410</v>
       </c>
       <c r="K3" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="L3" t="n">
-        <v>532</v>
+        <v>572</v>
       </c>
       <c r="M3" t="n">
-        <v>5311.970615745925</v>
+        <v>5145.767494246189</v>
       </c>
       <c r="N3" t="n">
-        <v>6.188440084457397</v>
+        <v>5.551252841949463</v>
       </c>
       <c r="O3" t="n">
-        <v>1645</v>
+        <v>1798</v>
       </c>
       <c r="P3" t="n">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="Q3" t="n">
-        <v>5036</v>
+        <v>5521</v>
       </c>
       <c r="R3" t="n">
-        <v>0.5127281861686864</v>
+        <v>0.4942464667757684</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4692523336174548</v>
+        <v>0.4498524687343315</v>
       </c>
     </row>
     <row r="4">
@@ -652,55 +652,55 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2576.256016975754</v>
+        <v>2407.974345625335</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5038759708404541</v>
+        <v>1.354024887084961</v>
       </c>
       <c r="E4" t="n">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="F4" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G4" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H4" t="n">
-        <v>3124.348332247241</v>
+        <v>2760.159749151271</v>
       </c>
       <c r="I4" t="n">
-        <v>1.83085298538208</v>
+        <v>12.83297801017761</v>
       </c>
       <c r="J4" t="n">
-        <v>459</v>
+        <v>428</v>
       </c>
       <c r="K4" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="L4" t="n">
-        <v>537</v>
+        <v>584</v>
       </c>
       <c r="M4" t="n">
-        <v>5327.761886613613</v>
+        <v>5124.043065738488</v>
       </c>
       <c r="N4" t="n">
-        <v>5.59663200378418</v>
+        <v>5.288721323013306</v>
       </c>
       <c r="O4" t="n">
-        <v>1714</v>
+        <v>1817</v>
       </c>
       <c r="P4" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="Q4" t="n">
-        <v>5352</v>
+        <v>5595</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5164468548324609</v>
+        <v>0.5300636011968621</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4135720779681629</v>
+        <v>0.4613316645195933</v>
       </c>
     </row>
     <row r="5">
@@ -713,55 +713,55 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2398.671639725221</v>
+        <v>2371.784395865645</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7783718109130859</v>
+        <v>1.040065050125122</v>
       </c>
       <c r="E5" t="n">
-        <v>401</v>
+        <v>361</v>
       </c>
       <c r="F5" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G5" t="n">
-        <v>132</v>
+        <v>98</v>
       </c>
       <c r="H5" t="n">
-        <v>2911.03962544702</v>
+        <v>2780.169061681023</v>
       </c>
       <c r="I5" t="n">
-        <v>1.508305788040161</v>
+        <v>13.38470506668091</v>
       </c>
       <c r="J5" t="n">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="K5" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="L5" t="n">
-        <v>510</v>
+        <v>623</v>
       </c>
       <c r="M5" t="n">
-        <v>5274.760894970527</v>
+        <v>5136.810779941938</v>
       </c>
       <c r="N5" t="n">
-        <v>4.911954164505005</v>
+        <v>5.377187013626099</v>
       </c>
       <c r="O5" t="n">
-        <v>1653</v>
+        <v>1752</v>
       </c>
       <c r="P5" t="n">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="Q5" t="n">
-        <v>5075</v>
+        <v>5441</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5452549058645768</v>
+        <v>0.5382768613695258</v>
       </c>
       <c r="S5" t="n">
-        <v>0.448119131196508</v>
+        <v>0.4587752633332451</v>
       </c>
     </row>
     <row r="6">
@@ -774,55 +774,55 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2796.69923045083</v>
+        <v>2652.491078803331</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5506298542022705</v>
+        <v>0.9443299770355225</v>
       </c>
       <c r="E6" t="n">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F6" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="G6" t="n">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="H6" t="n">
-        <v>2856.326000128633</v>
+        <v>2718.111415473216</v>
       </c>
       <c r="I6" t="n">
-        <v>1.640429735183716</v>
+        <v>11.31294322013855</v>
       </c>
       <c r="J6" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="K6" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="L6" t="n">
-        <v>499</v>
+        <v>596</v>
       </c>
       <c r="M6" t="n">
-        <v>5336.032961801302</v>
+        <v>5129.387199176806</v>
       </c>
       <c r="N6" t="n">
-        <v>4.72425389289856</v>
+        <v>5.024757146835327</v>
       </c>
       <c r="O6" t="n">
-        <v>1669</v>
+        <v>1783</v>
       </c>
       <c r="P6" t="n">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="Q6" t="n">
-        <v>5132</v>
+        <v>5560</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4758841914074798</v>
+        <v>0.4828834369865822</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4647098283357654</v>
+        <v>0.4700904201754482</v>
       </c>
     </row>
     <row r="7">
@@ -835,55 +835,55 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2688.389379904899</v>
+        <v>2619.513510131664</v>
       </c>
       <c r="D7" t="n">
-        <v>0.437824010848999</v>
+        <v>1.039041996002197</v>
       </c>
       <c r="E7" t="n">
-        <v>355</v>
+        <v>380</v>
       </c>
       <c r="F7" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G7" t="n">
-        <v>96</v>
+        <v>129</v>
       </c>
       <c r="H7" t="n">
-        <v>2679.972503431092</v>
+        <v>2855.923033083517</v>
       </c>
       <c r="I7" t="n">
-        <v>1.538029193878174</v>
+        <v>10.48500680923462</v>
       </c>
       <c r="J7" t="n">
-        <v>463</v>
+        <v>434</v>
       </c>
       <c r="K7" t="n">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="L7" t="n">
-        <v>523</v>
+        <v>595</v>
       </c>
       <c r="M7" t="n">
-        <v>5354.070835581339</v>
+        <v>5210.520866160029</v>
       </c>
       <c r="N7" t="n">
-        <v>7.354281902313232</v>
+        <v>5.061434030532837</v>
       </c>
       <c r="O7" t="n">
-        <v>1701</v>
+        <v>1822</v>
       </c>
       <c r="P7" t="n">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="Q7" t="n">
-        <v>5232</v>
+        <v>5757</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4978793776804791</v>
+        <v>0.4972645581089183</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4994514294392776</v>
+        <v>0.4518929860483925</v>
       </c>
     </row>
     <row r="8">
@@ -896,55 +896,55 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2405.245851882218</v>
+        <v>2473.261921945768</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5247688293457031</v>
+        <v>0.8922271728515625</v>
       </c>
       <c r="E8" t="n">
-        <v>405</v>
+        <v>365</v>
       </c>
       <c r="F8" t="n">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="G8" t="n">
-        <v>143</v>
+        <v>102</v>
       </c>
       <c r="H8" t="n">
-        <v>2948.200498029854</v>
+        <v>2939.434869453759</v>
       </c>
       <c r="I8" t="n">
-        <v>2.341186046600342</v>
+        <v>13.79673910140991</v>
       </c>
       <c r="J8" t="n">
-        <v>461</v>
+        <v>443</v>
       </c>
       <c r="K8" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L8" t="n">
-        <v>526</v>
+        <v>606</v>
       </c>
       <c r="M8" t="n">
-        <v>5256.531116675408</v>
+        <v>5108.475164436123</v>
       </c>
       <c r="N8" t="n">
-        <v>6.108461856842041</v>
+        <v>4.886216878890991</v>
       </c>
       <c r="O8" t="n">
-        <v>1653</v>
+        <v>1832</v>
       </c>
       <c r="P8" t="n">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="Q8" t="n">
-        <v>5097</v>
+        <v>5723</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5424271637521551</v>
+        <v>0.5158512389051091</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4391357279942255</v>
+        <v>0.4245964255797227</v>
       </c>
     </row>
     <row r="9">
@@ -957,55 +957,55 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2484.863089508744</v>
+        <v>2609.376214295493</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9783089160919189</v>
+        <v>0.9345970153808594</v>
       </c>
       <c r="E9" t="n">
-        <v>384</v>
+        <v>364</v>
       </c>
       <c r="F9" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G9" t="n">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="H9" t="n">
-        <v>2760.991608807973</v>
+        <v>2932.092358856725</v>
       </c>
       <c r="I9" t="n">
-        <v>1.515859842300415</v>
+        <v>11.43692493438721</v>
       </c>
       <c r="J9" t="n">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="K9" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="L9" t="n">
-        <v>497</v>
+        <v>582</v>
       </c>
       <c r="M9" t="n">
-        <v>5193.639079579846</v>
+        <v>5200.704412928892</v>
       </c>
       <c r="N9" t="n">
-        <v>5.45109224319458</v>
+        <v>5.747639656066895</v>
       </c>
       <c r="O9" t="n">
-        <v>1686</v>
+        <v>1782</v>
       </c>
       <c r="P9" t="n">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="Q9" t="n">
-        <v>5298</v>
+        <v>5612</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5215564556115125</v>
+        <v>0.4982648489291924</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4683897809411641</v>
+        <v>0.4362124577648411</v>
       </c>
     </row>
     <row r="10">
@@ -1018,55 +1018,55 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2261.078148758636</v>
+        <v>2654.762626318854</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4653990268707275</v>
+        <v>1.262802839279175</v>
       </c>
       <c r="E10" t="n">
-        <v>394</v>
+        <v>381</v>
       </c>
       <c r="F10" t="n">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="G10" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="H10" t="n">
-        <v>2883.62539036968</v>
+        <v>2924.009123296829</v>
       </c>
       <c r="I10" t="n">
-        <v>1.436793804168701</v>
+        <v>10.87285017967224</v>
       </c>
       <c r="J10" t="n">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="K10" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L10" t="n">
-        <v>501</v>
+        <v>590</v>
       </c>
       <c r="M10" t="n">
-        <v>5281.810608601513</v>
+        <v>5196.245973750418</v>
       </c>
       <c r="N10" t="n">
-        <v>5.248492002487183</v>
+        <v>5.017510890960693</v>
       </c>
       <c r="O10" t="n">
-        <v>1663</v>
+        <v>1845</v>
       </c>
       <c r="P10" t="n">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="Q10" t="n">
-        <v>5137</v>
+        <v>5637</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5719123012331352</v>
+        <v>0.4890998925513211</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4540460451812396</v>
+        <v>0.4372843129313199</v>
       </c>
     </row>
     <row r="11">
@@ -1079,25 +1079,25 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2556.110631004668</v>
+        <v>2610.559068244467</v>
       </c>
       <c r="D11" t="n">
-        <v>0.448016881942749</v>
+        <v>1.067995071411133</v>
       </c>
       <c r="E11" t="n">
-        <v>356</v>
+        <v>389</v>
       </c>
       <c r="F11" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G11" t="n">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="H11" t="n">
-        <v>2841.277738853171</v>
+        <v>2903.521245012168</v>
       </c>
       <c r="I11" t="n">
-        <v>1.419310808181763</v>
+        <v>13.54699993133545</v>
       </c>
       <c r="J11" t="n">
         <v>428</v>
@@ -1106,28 +1106,28 @@
         <v>77</v>
       </c>
       <c r="L11" t="n">
-        <v>504</v>
+        <v>583</v>
       </c>
       <c r="M11" t="n">
-        <v>5253.035521877136</v>
+        <v>5176.802987435978</v>
       </c>
       <c r="N11" t="n">
-        <v>4.774924039840698</v>
+        <v>5.18458104133606</v>
       </c>
       <c r="O11" t="n">
-        <v>1704</v>
+        <v>1873</v>
       </c>
       <c r="P11" t="n">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="Q11" t="n">
-        <v>5270</v>
+        <v>5774</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5134031322728884</v>
+        <v>0.4957198343108181</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4591169758856189</v>
+        <v>0.4391285022708089</v>
       </c>
     </row>
     <row r="12">
@@ -1140,55 +1140,55 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2558.05449066028</v>
+        <v>2501.976933288683</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5398006439208984</v>
+        <v>1.187741994857788</v>
       </c>
       <c r="E12" t="n">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F12" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G12" t="n">
+        <v>96</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2943.898281814358</v>
+      </c>
+      <c r="I12" t="n">
+        <v>13.22038125991821</v>
+      </c>
+      <c r="J12" t="n">
+        <v>432</v>
+      </c>
+      <c r="K12" t="n">
+        <v>78</v>
+      </c>
+      <c r="L12" t="n">
+        <v>603</v>
+      </c>
+      <c r="M12" t="n">
+        <v>5183.547142677494</v>
+      </c>
+      <c r="N12" t="n">
+        <v>4.944211006164551</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1862</v>
+      </c>
+      <c r="P12" t="n">
         <v>90</v>
       </c>
-      <c r="H12" t="n">
-        <v>2756.867335794249</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1.739270925521851</v>
-      </c>
-      <c r="J12" t="n">
-        <v>481</v>
-      </c>
-      <c r="K12" t="n">
-        <v>60</v>
-      </c>
-      <c r="L12" t="n">
-        <v>540</v>
-      </c>
-      <c r="M12" t="n">
-        <v>5302.828782193288</v>
-      </c>
-      <c r="N12" t="n">
-        <v>4.546872854232788</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1722</v>
-      </c>
-      <c r="P12" t="n">
-        <v>67</v>
-      </c>
       <c r="Q12" t="n">
-        <v>5265</v>
+        <v>5837</v>
       </c>
       <c r="R12" t="n">
-        <v>0.5176056788312425</v>
+        <v>0.5173233956552155</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4801138318755996</v>
+        <v>0.4320687743772066</v>
       </c>
     </row>
     <row r="13">
@@ -1201,55 +1201,55 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2364.232103413604</v>
+        <v>2553.297700476735</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4935140609741211</v>
+        <v>1.561012983322144</v>
       </c>
       <c r="E13" t="n">
-        <v>410</v>
+        <v>396</v>
       </c>
       <c r="F13" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G13" t="n">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="H13" t="n">
-        <v>2651.274067337346</v>
+        <v>2782.849137672601</v>
       </c>
       <c r="I13" t="n">
-        <v>1.491492033004761</v>
+        <v>13.12834787368774</v>
       </c>
       <c r="J13" t="n">
-        <v>469</v>
+        <v>422</v>
       </c>
       <c r="K13" t="n">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="L13" t="n">
-        <v>527</v>
+        <v>566</v>
       </c>
       <c r="M13" t="n">
-        <v>5417.274361563551</v>
+        <v>5148.773796119109</v>
       </c>
       <c r="N13" t="n">
-        <v>5.035845041275024</v>
+        <v>4.842334032058716</v>
       </c>
       <c r="O13" t="n">
-        <v>1642</v>
+        <v>1821</v>
       </c>
       <c r="P13" t="n">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="Q13" t="n">
-        <v>4970</v>
+        <v>5616</v>
       </c>
       <c r="R13" t="n">
-        <v>0.5635753433150408</v>
+        <v>0.5040959650623446</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5105889252815825</v>
+        <v>0.4595122551761402</v>
       </c>
     </row>
     <row r="14">
@@ -1262,55 +1262,55 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2547.484804307749</v>
+        <v>2475.577882942801</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4166629314422607</v>
+        <v>1.409417152404785</v>
       </c>
       <c r="E14" t="n">
-        <v>342</v>
+        <v>384</v>
       </c>
       <c r="F14" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G14" t="n">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="H14" t="n">
-        <v>2870.074761809452</v>
+        <v>2847.515826845597</v>
       </c>
       <c r="I14" t="n">
-        <v>1.498515844345093</v>
+        <v>10.89860391616821</v>
       </c>
       <c r="J14" t="n">
-        <v>466</v>
+        <v>414</v>
       </c>
       <c r="K14" t="n">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="L14" t="n">
-        <v>528</v>
+        <v>570</v>
       </c>
       <c r="M14" t="n">
-        <v>5275.334581740795</v>
+        <v>5194.135304437428</v>
       </c>
       <c r="N14" t="n">
-        <v>4.732311725616455</v>
+        <v>4.964370250701904</v>
       </c>
       <c r="O14" t="n">
-        <v>1719</v>
+        <v>1834</v>
       </c>
       <c r="P14" t="n">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="Q14" t="n">
-        <v>5379</v>
+        <v>5757</v>
       </c>
       <c r="R14" t="n">
-        <v>0.5170951216771713</v>
+        <v>0.5233897967910314</v>
       </c>
       <c r="S14" t="n">
-        <v>0.455944506014183</v>
+        <v>0.4517825085509572</v>
       </c>
     </row>
     <row r="15">
@@ -1323,55 +1323,55 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2366.245251365809</v>
+        <v>2709.426162543324</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5896492004394531</v>
+        <v>1.027628660202026</v>
       </c>
       <c r="E15" t="n">
-        <v>387</v>
+        <v>369</v>
       </c>
       <c r="F15" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="G15" t="n">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="H15" t="n">
-        <v>2839.181362475413</v>
+        <v>2971.221071904821</v>
       </c>
       <c r="I15" t="n">
-        <v>1.529403209686279</v>
+        <v>14.87120413780212</v>
       </c>
       <c r="J15" t="n">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="K15" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="L15" t="n">
-        <v>508</v>
+        <v>601</v>
       </c>
       <c r="M15" t="n">
-        <v>5243.902928468458</v>
+        <v>5212.737820662083</v>
       </c>
       <c r="N15" t="n">
-        <v>4.94625186920166</v>
+        <v>5.038378000259399</v>
       </c>
       <c r="O15" t="n">
-        <v>1620</v>
+        <v>1851</v>
       </c>
       <c r="P15" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="Q15" t="n">
-        <v>5067</v>
+        <v>5831</v>
       </c>
       <c r="R15" t="n">
-        <v>0.5487625755771002</v>
+        <v>0.4802297265356821</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4585747674576752</v>
+        <v>0.4300075748817465</v>
       </c>
     </row>
     <row r="16">
@@ -1384,55 +1384,55 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2513.64669394969</v>
+        <v>2532.276454790017</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5663940906524658</v>
+        <v>1.07986307144165</v>
       </c>
       <c r="E16" t="n">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="F16" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="G16" t="n">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="H16" t="n">
-        <v>2815.767189338111</v>
+        <v>3007.64558078161</v>
       </c>
       <c r="I16" t="n">
-        <v>1.659443855285645</v>
+        <v>14.54470086097717</v>
       </c>
       <c r="J16" t="n">
-        <v>459</v>
+        <v>444</v>
       </c>
       <c r="K16" t="n">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="L16" t="n">
-        <v>526</v>
+        <v>617</v>
       </c>
       <c r="M16" t="n">
-        <v>5246.257653326491</v>
+        <v>5037.883841421361</v>
       </c>
       <c r="N16" t="n">
-        <v>4.423005819320679</v>
+        <v>4.535847902297974</v>
       </c>
       <c r="O16" t="n">
-        <v>1645</v>
+        <v>1886</v>
       </c>
       <c r="P16" t="n">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="Q16" t="n">
-        <v>5052</v>
+        <v>5904</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5208686152964936</v>
+        <v>0.4973531477701609</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4632808040694075</v>
+        <v>0.4029942580150778</v>
       </c>
     </row>
     <row r="17">
@@ -1445,55 +1445,55 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2566.138668318003</v>
+        <v>2562.766288386945</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4382212162017822</v>
+        <v>0.9019389152526855</v>
       </c>
       <c r="E17" t="n">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F17" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G17" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="H17" t="n">
-        <v>2711.022572272212</v>
+        <v>2765.006387540994</v>
       </c>
       <c r="I17" t="n">
-        <v>1.538365840911865</v>
+        <v>14.18367409706116</v>
       </c>
       <c r="J17" t="n">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="K17" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="L17" t="n">
-        <v>523</v>
+        <v>592</v>
       </c>
       <c r="M17" t="n">
-        <v>5339.765014619631</v>
+        <v>5150.231803292889</v>
       </c>
       <c r="N17" t="n">
-        <v>4.830703973770142</v>
+        <v>4.832599878311157</v>
       </c>
       <c r="O17" t="n">
-        <v>1664</v>
+        <v>1818</v>
       </c>
       <c r="P17" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="Q17" t="n">
-        <v>5107</v>
+        <v>5684</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5194285401525676</v>
+        <v>0.5023978752279855</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4922955289512255</v>
+        <v>0.4631297205354641</v>
       </c>
     </row>
     <row r="18">
@@ -1506,55 +1506,55 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2739.070376848465</v>
+        <v>2718.65141965389</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4201390743255615</v>
+        <v>0.9596500396728516</v>
       </c>
       <c r="E18" t="n">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="F18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G18" t="n">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="H18" t="n">
-        <v>2868.898837485696</v>
+        <v>2816.929863965978</v>
       </c>
       <c r="I18" t="n">
-        <v>1.437104940414429</v>
+        <v>14.77461576461792</v>
       </c>
       <c r="J18" t="n">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="K18" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L18" t="n">
-        <v>499</v>
+        <v>591</v>
       </c>
       <c r="M18" t="n">
-        <v>5269.560469296507</v>
+        <v>5110.415945299152</v>
       </c>
       <c r="N18" t="n">
-        <v>4.881451845169067</v>
+        <v>4.624592304229736</v>
       </c>
       <c r="O18" t="n">
-        <v>1675</v>
+        <v>1832</v>
       </c>
       <c r="P18" t="n">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="Q18" t="n">
-        <v>5106</v>
+        <v>5617</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4802089485816007</v>
+        <v>0.468017584330947</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4555715122349288</v>
+        <v>0.4487865774297395</v>
       </c>
     </row>
     <row r="19">
@@ -1567,55 +1567,55 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2460.344533277646</v>
+        <v>2471.30973609554</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5659871101379395</v>
+        <v>1.152847051620483</v>
       </c>
       <c r="E19" t="n">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F19" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G19" t="n">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="H19" t="n">
-        <v>2890.190559246736</v>
+        <v>2774.300916380535</v>
       </c>
       <c r="I19" t="n">
-        <v>1.644323110580444</v>
+        <v>12.74045014381409</v>
       </c>
       <c r="J19" t="n">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="K19" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="L19" t="n">
-        <v>507</v>
+        <v>596</v>
       </c>
       <c r="M19" t="n">
-        <v>5265.869172002565</v>
+        <v>5229.267106670539</v>
       </c>
       <c r="N19" t="n">
-        <v>4.748901128768921</v>
+        <v>5.182266235351562</v>
       </c>
       <c r="O19" t="n">
-        <v>1609</v>
+        <v>1808</v>
       </c>
       <c r="P19" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="Q19" t="n">
-        <v>4899</v>
+        <v>5604</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5327752260996643</v>
+        <v>0.5274080123114964</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4511465315900318</v>
+        <v>0.4694665887612452</v>
       </c>
     </row>
     <row r="20">
@@ -1628,55 +1628,55 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2538.341432851887</v>
+        <v>2474.967896204232</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6471128463745117</v>
+        <v>0.9380106925964355</v>
       </c>
       <c r="E20" t="n">
-        <v>406</v>
+        <v>360</v>
       </c>
       <c r="F20" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G20" t="n">
-        <v>144</v>
+        <v>107</v>
       </c>
       <c r="H20" t="n">
-        <v>2894.098551645862</v>
+        <v>2839.928118512381</v>
       </c>
       <c r="I20" t="n">
-        <v>1.618371248245239</v>
+        <v>15.00557088851929</v>
       </c>
       <c r="J20" t="n">
-        <v>407</v>
+        <v>467</v>
       </c>
       <c r="K20" t="n">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="L20" t="n">
-        <v>484</v>
+        <v>625</v>
       </c>
       <c r="M20" t="n">
-        <v>5253.323692851477</v>
+        <v>5318.10972789795</v>
       </c>
       <c r="N20" t="n">
-        <v>4.621283054351807</v>
+        <v>4.804755926132202</v>
       </c>
       <c r="O20" t="n">
-        <v>1655</v>
+        <v>1771</v>
       </c>
       <c r="P20" t="n">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="Q20" t="n">
-        <v>5151</v>
+        <v>5529</v>
       </c>
       <c r="R20" t="n">
-        <v>0.516812292319629</v>
+        <v>0.5346151127305727</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4490919043149689</v>
+        <v>0.4659891834095536</v>
       </c>
     </row>
     <row r="21">
@@ -1689,55 +1689,55 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2762.628961054956</v>
+        <v>2419.823018663574</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4268133640289307</v>
+        <v>1.147511005401611</v>
       </c>
       <c r="E21" t="n">
-        <v>341</v>
+        <v>408</v>
       </c>
       <c r="F21" t="n">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="G21" t="n">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="H21" t="n">
-        <v>2880.639775422643</v>
+        <v>2837.566490593729</v>
       </c>
       <c r="I21" t="n">
-        <v>1.417731285095215</v>
+        <v>11.27724099159241</v>
       </c>
       <c r="J21" t="n">
-        <v>422</v>
+        <v>438</v>
       </c>
       <c r="K21" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="L21" t="n">
-        <v>494</v>
+        <v>580</v>
       </c>
       <c r="M21" t="n">
-        <v>5176.278342923514</v>
+        <v>5204.219126693463</v>
       </c>
       <c r="N21" t="n">
-        <v>5.015410184860229</v>
+        <v>5.082929849624634</v>
       </c>
       <c r="O21" t="n">
-        <v>1681</v>
+        <v>1838</v>
       </c>
       <c r="P21" t="n">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="Q21" t="n">
-        <v>5231</v>
+        <v>5765</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4662904932784876</v>
+        <v>0.5350266851271066</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4434921029003854</v>
+        <v>0.4547565309002281</v>
       </c>
     </row>
     <row r="22">
@@ -1750,55 +1750,55 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2466.906839333565</v>
+        <v>2609.245997484461</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4971168041229248</v>
+        <v>1.102654933929443</v>
       </c>
       <c r="E22" t="n">
-        <v>397</v>
+        <v>380</v>
       </c>
       <c r="F22" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G22" t="n">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="H22" t="n">
-        <v>2953.578834866332</v>
+        <v>2707.76222926328</v>
       </c>
       <c r="I22" t="n">
-        <v>1.488696813583374</v>
+        <v>12.00327491760254</v>
       </c>
       <c r="J22" t="n">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="K22" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="L22" t="n">
-        <v>514</v>
+        <v>584</v>
       </c>
       <c r="M22" t="n">
-        <v>5291.441043069452</v>
+        <v>5119.080374748842</v>
       </c>
       <c r="N22" t="n">
-        <v>4.911229848861694</v>
+        <v>5.55678915977478</v>
       </c>
       <c r="O22" t="n">
-        <v>1692</v>
+        <v>1886</v>
       </c>
       <c r="P22" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="Q22" t="n">
-        <v>5279</v>
+        <v>5933</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5337930028409492</v>
+        <v>0.4902900899241147</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4418195703541233</v>
+        <v>0.4710451817439706</v>
       </c>
     </row>
     <row r="23">
@@ -1811,55 +1811,55 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2677.542684745007</v>
+        <v>2508.126558006198</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4539558887481689</v>
+        <v>1.068467140197754</v>
       </c>
       <c r="E23" t="n">
-        <v>314</v>
+        <v>360</v>
       </c>
       <c r="F23" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G23" t="n">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="H23" t="n">
-        <v>2845.337854111692</v>
+        <v>2882.841337429923</v>
       </c>
       <c r="I23" t="n">
-        <v>2.026116132736206</v>
+        <v>15.02917623519897</v>
       </c>
       <c r="J23" t="n">
-        <v>428</v>
+        <v>458</v>
       </c>
       <c r="K23" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L23" t="n">
-        <v>500</v>
+        <v>628</v>
       </c>
       <c r="M23" t="n">
-        <v>5320.253028273772</v>
+        <v>5154.518768808332</v>
       </c>
       <c r="N23" t="n">
-        <v>4.528721809387207</v>
+        <v>4.981268882751465</v>
       </c>
       <c r="O23" t="n">
-        <v>1663</v>
+        <v>1848</v>
       </c>
       <c r="P23" t="n">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="Q23" t="n">
-        <v>5154</v>
+        <v>5686</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4967264394164027</v>
+        <v>0.5134120816120243</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4651874940927574</v>
+        <v>0.4407157163002428</v>
       </c>
     </row>
     <row r="24">
@@ -1872,55 +1872,55 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2678.319498542277</v>
+        <v>2525.31373293145</v>
       </c>
       <c r="D24" t="n">
-        <v>0.483206033706665</v>
+        <v>1.025272130966187</v>
       </c>
       <c r="E24" t="n">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="F24" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G24" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H24" t="n">
-        <v>2984.457911067236</v>
+        <v>2802.792598903211</v>
       </c>
       <c r="I24" t="n">
-        <v>1.86084771156311</v>
+        <v>14.31016492843628</v>
       </c>
       <c r="J24" t="n">
-        <v>463</v>
+        <v>419</v>
       </c>
       <c r="K24" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="L24" t="n">
-        <v>529</v>
+        <v>579</v>
       </c>
       <c r="M24" t="n">
-        <v>5269.939493985619</v>
+        <v>5212.461514190602</v>
       </c>
       <c r="N24" t="n">
-        <v>4.639792919158936</v>
+        <v>4.989542961120605</v>
       </c>
       <c r="O24" t="n">
-        <v>1671</v>
+        <v>1895</v>
       </c>
       <c r="P24" t="n">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="Q24" t="n">
-        <v>5171</v>
+        <v>5868</v>
       </c>
       <c r="R24" t="n">
-        <v>0.4917741462498875</v>
+        <v>0.5155237643373595</v>
       </c>
       <c r="S24" t="n">
-        <v>0.4336826989240989</v>
+        <v>0.4622900157108532</v>
       </c>
     </row>
     <row r="25">
@@ -1933,55 +1933,55 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2374.596639560027</v>
+        <v>2687.951669616055</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4491848945617676</v>
+        <v>1.081377983093262</v>
       </c>
       <c r="E25" t="n">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="F25" t="n">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="G25" t="n">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="H25" t="n">
-        <v>2894.52780166608</v>
+        <v>2678.960217125135</v>
       </c>
       <c r="I25" t="n">
-        <v>1.520729780197144</v>
+        <v>11.21876811981201</v>
       </c>
       <c r="J25" t="n">
-        <v>454</v>
+        <v>401</v>
       </c>
       <c r="K25" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="L25" t="n">
-        <v>523</v>
+        <v>559</v>
       </c>
       <c r="M25" t="n">
-        <v>5309.139128341405</v>
+        <v>5037.834938673008</v>
       </c>
       <c r="N25" t="n">
-        <v>5.174187898635864</v>
+        <v>5.708893775939941</v>
       </c>
       <c r="O25" t="n">
-        <v>1622</v>
+        <v>1858</v>
       </c>
       <c r="P25" t="n">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="Q25" t="n">
-        <v>4910</v>
+        <v>5928</v>
       </c>
       <c r="R25" t="n">
-        <v>0.5527341472586611</v>
+        <v>0.4664470546698626</v>
       </c>
       <c r="S25" t="n">
-        <v>0.454802797271892</v>
+        <v>0.4682318397214523</v>
       </c>
     </row>
     <row r="26">
@@ -1994,55 +1994,55 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2720.34016308618</v>
+        <v>2527.497597142011</v>
       </c>
       <c r="D26" t="n">
-        <v>0.404088020324707</v>
+        <v>1.042350053787231</v>
       </c>
       <c r="E26" t="n">
-        <v>321</v>
+        <v>368</v>
       </c>
       <c r="F26" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G26" t="n">
-        <v>84</v>
+        <v>135</v>
       </c>
       <c r="H26" t="n">
-        <v>2958.564639764021</v>
+        <v>2838.105065880984</v>
       </c>
       <c r="I26" t="n">
-        <v>1.427681922912598</v>
+        <v>11.89603400230408</v>
       </c>
       <c r="J26" t="n">
-        <v>433</v>
+        <v>447</v>
       </c>
       <c r="K26" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L26" t="n">
-        <v>504</v>
+        <v>597</v>
       </c>
       <c r="M26" t="n">
-        <v>5297.08658630588</v>
+        <v>5142.996991857456</v>
       </c>
       <c r="N26" t="n">
-        <v>4.95252513885498</v>
+        <v>5.207188367843628</v>
       </c>
       <c r="O26" t="n">
-        <v>1637</v>
+        <v>1845</v>
       </c>
       <c r="P26" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q26" t="n">
-        <v>5102</v>
+        <v>5708</v>
       </c>
       <c r="R26" t="n">
-        <v>0.4864459701076341</v>
+        <v>0.5085554976711789</v>
       </c>
       <c r="S26" t="n">
-        <v>0.4414732340957851</v>
+        <v>0.44816124326451</v>
       </c>
     </row>
     <row r="27">
@@ -2055,55 +2055,55 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2627.512202844061</v>
+        <v>2693.254013325326</v>
       </c>
       <c r="D27" t="n">
-        <v>0.4484536647796631</v>
+        <v>1.132729291915894</v>
       </c>
       <c r="E27" t="n">
-        <v>368</v>
+        <v>351</v>
       </c>
       <c r="F27" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G27" t="n">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="H27" t="n">
-        <v>2735.0073663137</v>
+        <v>2829.259985763343</v>
       </c>
       <c r="I27" t="n">
-        <v>1.567209005355835</v>
+        <v>12.02052307128906</v>
       </c>
       <c r="J27" t="n">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="K27" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="L27" t="n">
-        <v>496</v>
+        <v>592</v>
       </c>
       <c r="M27" t="n">
-        <v>5242.086851086267</v>
+        <v>5157.629720066634</v>
       </c>
       <c r="N27" t="n">
-        <v>4.377427816390991</v>
+        <v>5.120990991592407</v>
       </c>
       <c r="O27" t="n">
-        <v>1667</v>
+        <v>1835</v>
       </c>
       <c r="P27" t="n">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="Q27" t="n">
-        <v>5118</v>
+        <v>5787</v>
       </c>
       <c r="R27" t="n">
-        <v>0.4987659919637564</v>
+        <v>0.4778116771650427</v>
       </c>
       <c r="S27" t="n">
-        <v>0.4782598144578716</v>
+        <v>0.4514418174000303</v>
       </c>
     </row>
     <row r="28">
@@ -2116,55 +2116,55 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2725.620496556971</v>
+        <v>2591.214560490653</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4611499309539795</v>
+        <v>1.515078783035278</v>
       </c>
       <c r="E28" t="n">
-        <v>368</v>
+        <v>388</v>
       </c>
       <c r="F28" t="n">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="G28" t="n">
-        <v>109</v>
+        <v>140</v>
       </c>
       <c r="H28" t="n">
-        <v>2959.969455991751</v>
+        <v>2945.879413712051</v>
       </c>
       <c r="I28" t="n">
-        <v>1.557024955749512</v>
+        <v>11.5784170627594</v>
       </c>
       <c r="J28" t="n">
-        <v>415</v>
+        <v>435</v>
       </c>
       <c r="K28" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="L28" t="n">
-        <v>493</v>
+        <v>591</v>
       </c>
       <c r="M28" t="n">
-        <v>5278.617127257987</v>
+        <v>5252.703235467295</v>
       </c>
       <c r="N28" t="n">
-        <v>4.88388991355896</v>
+        <v>4.790850639343262</v>
       </c>
       <c r="O28" t="n">
-        <v>1571</v>
+        <v>1828</v>
       </c>
       <c r="P28" t="n">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="Q28" t="n">
-        <v>4957</v>
+        <v>5714</v>
       </c>
       <c r="R28" t="n">
-        <v>0.4836487604902663</v>
+        <v>0.5066893284596286</v>
       </c>
       <c r="S28" t="n">
-        <v>0.439252860241196</v>
+        <v>0.4391688847333144</v>
       </c>
     </row>
     <row r="29">
@@ -2177,55 +2177,55 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2671.777668936787</v>
+        <v>2755.190739469014</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4229111671447754</v>
+        <v>0.9665641784667969</v>
       </c>
       <c r="E29" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="F29" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G29" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H29" t="n">
-        <v>2937.447135439365</v>
+        <v>2715.234458600121</v>
       </c>
       <c r="I29" t="n">
-        <v>1.520287990570068</v>
+        <v>13.77458000183105</v>
       </c>
       <c r="J29" t="n">
-        <v>454</v>
+        <v>424</v>
       </c>
       <c r="K29" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="L29" t="n">
-        <v>526</v>
+        <v>580</v>
       </c>
       <c r="M29" t="n">
-        <v>5316.412097756505</v>
+        <v>5137.354868047086</v>
       </c>
       <c r="N29" t="n">
-        <v>4.903427124023438</v>
+        <v>4.915681123733521</v>
       </c>
       <c r="O29" t="n">
-        <v>1698</v>
+        <v>1847</v>
       </c>
       <c r="P29" t="n">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="Q29" t="n">
-        <v>5265</v>
+        <v>5876</v>
       </c>
       <c r="R29" t="n">
-        <v>0.4974472219592868</v>
+        <v>0.463694681361116</v>
       </c>
       <c r="S29" t="n">
-        <v>0.4474756506029789</v>
+        <v>0.4714722793459097</v>
       </c>
     </row>
     <row r="30">
@@ -2238,55 +2238,55 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2564.491106386962</v>
+        <v>2533.853928027262</v>
       </c>
       <c r="D30" t="n">
-        <v>0.4153399467468262</v>
+        <v>1.203792095184326</v>
       </c>
       <c r="E30" t="n">
-        <v>324</v>
+        <v>357</v>
       </c>
       <c r="F30" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="G30" t="n">
-        <v>91</v>
+        <v>129</v>
       </c>
       <c r="H30" t="n">
-        <v>2839.540564369555</v>
+        <v>2681.048351521721</v>
       </c>
       <c r="I30" t="n">
-        <v>1.404078006744385</v>
+        <v>13.7210750579834</v>
       </c>
       <c r="J30" t="n">
-        <v>424</v>
+        <v>442</v>
       </c>
       <c r="K30" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="L30" t="n">
-        <v>495</v>
+        <v>590</v>
       </c>
       <c r="M30" t="n">
-        <v>5281.924091903931</v>
+        <v>5133.567645525111</v>
       </c>
       <c r="N30" t="n">
-        <v>4.659160852432251</v>
+        <v>5.085721015930176</v>
       </c>
       <c r="O30" t="n">
-        <v>1714</v>
+        <v>1875</v>
       </c>
       <c r="P30" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="Q30" t="n">
-        <v>5319</v>
+        <v>5855</v>
       </c>
       <c r="R30" t="n">
-        <v>0.5144778565981698</v>
+        <v>0.506414621761924</v>
       </c>
       <c r="S30" t="n">
-        <v>0.4624041324785473</v>
+        <v>0.4777416922013741</v>
       </c>
     </row>
     <row r="31">
@@ -2299,55 +2299,55 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2604.371185919748</v>
+        <v>2510.922653058738</v>
       </c>
       <c r="D31" t="n">
-        <v>0.529177188873291</v>
+        <v>1.183777093887329</v>
       </c>
       <c r="E31" t="n">
-        <v>357</v>
+        <v>372</v>
       </c>
       <c r="F31" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G31" t="n">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="H31" t="n">
-        <v>3031.552161918056</v>
+        <v>2583.91067818376</v>
       </c>
       <c r="I31" t="n">
-        <v>1.657168865203857</v>
+        <v>12.11643123626709</v>
       </c>
       <c r="J31" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K31" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="L31" t="n">
-        <v>513</v>
+        <v>578</v>
       </c>
       <c r="M31" t="n">
-        <v>5351.25720495756</v>
+        <v>5061.146243302657</v>
       </c>
       <c r="N31" t="n">
-        <v>4.485888004302979</v>
+        <v>5.06554913520813</v>
       </c>
       <c r="O31" t="n">
-        <v>1654</v>
+        <v>1853</v>
       </c>
       <c r="P31" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="Q31" t="n">
-        <v>5123</v>
+        <v>5774</v>
       </c>
       <c r="R31" t="n">
-        <v>0.5133160141308508</v>
+        <v>0.5038826122874032</v>
       </c>
       <c r="S31" t="n">
-        <v>0.4334878616730404</v>
+        <v>0.4894613682418263</v>
       </c>
     </row>
   </sheetData>
